--- a/Controle de horas.xlsx
+++ b/Controle de horas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MConti\Pessoal\Dexian\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEDFEFE7-2351-4109-BCC7-2575AF25F554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F91E837-029E-46A6-942A-896F887F68D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{F7D781DF-D6B8-4C74-83A5-E25C6E6C9748}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{F7D781DF-D6B8-4C74-83A5-E25C6E6C9748}"/>
   </bookViews>
   <sheets>
     <sheet name="Maio" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="79">
   <si>
     <t>Dia</t>
   </si>
@@ -206,17 +206,93 @@
   </si>
   <si>
     <t>Migração de notebooks de ingestão de tabelas do Marketing.</t>
+  </si>
+  <si>
+    <t>Migração de notebooks de ingestão de tabelas do Marketing. Apoio na implantação de jobs em prod.</t>
+  </si>
+  <si>
+    <t>Implantação de jobs em produção.</t>
+  </si>
+  <si>
+    <t>Implantação de jobs em produção. Criação automatizada de schema pelo Framework</t>
+  </si>
+  <si>
+    <t>Migração de tabelas do Marketing - Parte 2 (3 tab. + 11 views)</t>
+  </si>
+  <si>
+    <t>Corrigir ingestões projeto peças em produção - Produção</t>
+  </si>
+  <si>
+    <t>Corrigir ingestões projeto peças em produção - Produção. Banco de Horas - Negociado com Cassita.</t>
+  </si>
+  <si>
+    <t>Ajuste dm_calendário, carregar 2 anos das tabelas de peças</t>
+  </si>
+  <si>
+    <t>Café com dados. Carregar 2 anos das tabelas de peças</t>
+  </si>
+  <si>
+    <t>Projeto peças, segunda parte (7 tabelas)</t>
+  </si>
+  <si>
+    <t>Projeto peças, segunda parte (7 tabelas). Framework - Escrita com partição ano, mês e dia</t>
+  </si>
+  <si>
+    <t>Framework - Escrita com partição ano, mês e dia</t>
+  </si>
+  <si>
+    <t>Ausência por problemas de saúde</t>
+  </si>
+  <si>
+    <t>Migração de tabelas do Marketing - Parte 2 (3 tab. + 11 views). Apoio à Marlo e Wagner</t>
+  </si>
+  <si>
+    <t>Selecionar Versão + recente do Framework. Implantar projeto peças em produção</t>
+  </si>
+  <si>
+    <t>Framework - Escrita com partição ano, mês e dia. Atuação reduzida por problemas de saúde</t>
+  </si>
+  <si>
+    <t>Framework - Escrita com partição ano, mês e dia. Análise query do Relat. 2098 - Compensação ausência</t>
+  </si>
+  <si>
+    <t>Framework - Escrita com partição ano, mês e dia. Reprocessar Grupo 0.Relat 6020 - Compensação ausência</t>
+  </si>
+  <si>
+    <t>Framework - Escrita com partição ano, mês e dia. Reprocessar Grupo 0.Relat 6020 e Grupo 1 - Compensação ausência</t>
+  </si>
+  <si>
+    <t>Framework - Escrita com partição ano, mês e dia. Reprocessar Grupo 1 e Grupo 2 - Compensação ausência</t>
+  </si>
+  <si>
+    <t>Framework - Escrita com partição ano, mês e dia. Reprocessar Grupo 2 - Compensação ausência</t>
+  </si>
+  <si>
+    <t>Framework - Escrita com partição ano, mês e dia. Reprocessar Grupo 3 - Compensação ausência</t>
+  </si>
+  <si>
+    <t>Framework - Escrita com partição ano, mês e dia. Reprocessar Grupo 4</t>
+  </si>
+  <si>
+    <t>Horas - Faturar</t>
+  </si>
+  <si>
+    <t>Horas</t>
+  </si>
+  <si>
+    <t>Diferença</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="[h]:mm"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -252,6 +328,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="2" tint="-0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -274,7 +357,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -287,6 +370,13 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2908,12 +2998,21 @@
       <c r="D31" s="2">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
+      <c r="E31" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G31" s="2">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="H31" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.37500000000000006</v>
+      </c>
+      <c r="I31" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
@@ -2928,16 +3027,27 @@
         <f>_xlfn.XLOOKUP(WEEKDAY(A32),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
+      <c r="D32" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G32" s="2">
+        <v>0.75</v>
+      </c>
       <c r="H32" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+        <v>0.43750000000000006</v>
+      </c>
+      <c r="I32" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>45869</v>
       </c>
@@ -2949,19 +3059,30 @@
         <f>_xlfn.XLOOKUP(WEEKDAY(A33),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
+      <c r="D33" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G33" s="2">
+        <v>0.75</v>
+      </c>
       <c r="H33" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="H34" s="6"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>14</v>
       </c>
@@ -2971,10 +3092,10 @@
       </c>
       <c r="H35" s="6">
         <f>SUM(H3:H33)</f>
-        <v>7.2361111111111125</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+        <v>8.4652777777777786</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>15</v>
       </c>
@@ -2982,25 +3103,31 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B37">
         <f>B35-B36</f>
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B38">
         <f>(B37)*8</f>
         <v>176</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B39">
         <f>B38+5</f>
         <v>181</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B40">
+        <f>B39*105</f>
+        <v>19005</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B41" s="9"/>
     </row>
   </sheetData>
@@ -3011,7 +3138,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3883A76-0B02-401D-9BF6-6EAEBFF623DD}">
-  <dimension ref="A2:I35"/>
+  <dimension ref="A2:K37"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
@@ -3019,10 +3146,13 @@
     <col min="3" max="3" width="10.6328125" hidden="1" customWidth="1"/>
     <col min="4" max="6" width="10.6328125" customWidth="1"/>
     <col min="7" max="7" width="10.1796875" customWidth="1"/>
-    <col min="8" max="8" width="32.81640625" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="87.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -3042,13 +3172,19 @@
         <v>2</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="I2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>45870</v>
       </c>
@@ -3060,34 +3196,90 @@
         <f>_xlfn.XLOOKUP(WEEKDAY(A3),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
+      <c r="D3" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="H3" s="2">
+        <f>IF((AND(D3&lt;&gt;"",E3&lt;&gt;"")),(E3-D3),"00:00") + IF((AND(F3&lt;&gt;"",G3&lt;&gt;"")),(G3-F3),"00:00")</f>
+        <v>0.37500000000000006</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J3" s="14">
+        <f>(H3*24)-(I3*24)</f>
+        <v>1.0000000000000018</v>
+      </c>
+      <c r="K3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4" s="10">
         <v>45871</v>
       </c>
-      <c r="B4" t="str">
+      <c r="B4" s="11" t="str">
         <f>_xlfn.XLOOKUP(WEEKDAY(A4),Auxilar!$A$2:$A$8,Auxilar!$B$2:$B$8,FALSE)</f>
         <v>Sábado</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="11">
         <f>_xlfn.XLOOKUP(WEEKDAY(A4),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="12">
+        <f t="shared" ref="H4:H5" si="0">IF((AND(D4&lt;&gt;"",E4&lt;&gt;"")),(E4-D4),"00:00") + IF((AND(F4&lt;&gt;"",G4&lt;&gt;"")),(G4-F4),"00:00")</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="14">
+        <f t="shared" ref="J4:J31" si="1">(H4*24)-(I4*24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5" s="10">
         <v>45872</v>
       </c>
-      <c r="B5" t="str">
+      <c r="B5" s="11" t="str">
         <f>_xlfn.XLOOKUP(WEEKDAY(A5),Auxilar!$A$2:$A$8,Auxilar!$B$2:$B$8,FALSE)</f>
         <v>Domingo</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="11">
         <f>_xlfn.XLOOKUP(WEEKDAY(A5),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>45873</v>
       </c>
@@ -3099,8 +3291,34 @@
         <f>_xlfn.XLOOKUP(WEEKDAY(A6),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="D6" s="2">
+        <v>0.31944444444444442</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="H6" s="2">
+        <f>IF((AND(D6&lt;&gt;"",E6&lt;&gt;"")),(E6-D6),"00:00") + IF((AND(F6&lt;&gt;"",G6&lt;&gt;"")),(G6-F6),"00:00")</f>
+        <v>0.37500000000000006</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J6" s="14">
+        <f t="shared" si="1"/>
+        <v>1.0000000000000018</v>
+      </c>
+      <c r="K6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>45874</v>
       </c>
@@ -3112,8 +3330,34 @@
         <f>_xlfn.XLOOKUP(WEEKDAY(A7),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="D7" s="2">
+        <v>0.30555555555555558</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="H7" s="2">
+        <f t="shared" ref="H7:I33" si="2">IF((AND(D7&lt;&gt;"",E7&lt;&gt;"")),(E7-D7),"00:00") + IF((AND(F7&lt;&gt;"",G7&lt;&gt;"")),(G7-F7),"00:00")</f>
+        <v>0.36111111111111116</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J7" s="14">
+        <f t="shared" si="1"/>
+        <v>0.66666666666666785</v>
+      </c>
+      <c r="K7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>45875</v>
       </c>
@@ -3125,8 +3369,34 @@
         <f>_xlfn.XLOOKUP(WEEKDAY(A8),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="D8" s="2">
+        <v>0.30555555555555558</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" si="2"/>
+        <v>0.42361111111111116</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J8" s="14">
+        <f t="shared" si="1"/>
+        <v>2.1666666666666679</v>
+      </c>
+      <c r="K8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>45876</v>
       </c>
@@ -3138,8 +3408,34 @@
         <f>_xlfn.XLOOKUP(WEEKDAY(A9),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="D9" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H9" s="2">
+        <f t="shared" si="2"/>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J9" s="14">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="K9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>45877</v>
       </c>
@@ -3151,34 +3447,102 @@
         <f>_xlfn.XLOOKUP(WEEKDAY(A10),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="1">
+      <c r="D10" s="2">
+        <v>0.34722222222222221</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="2"/>
+        <v>0.42361111111111116</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J10" s="14">
+        <f t="shared" si="1"/>
+        <v>2.1666666666666679</v>
+      </c>
+      <c r="K10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11" s="10">
         <v>45878</v>
       </c>
-      <c r="B11" t="str">
+      <c r="B11" s="11" t="str">
         <f>_xlfn.XLOOKUP(WEEKDAY(A11),Auxilar!$A$2:$A$8,Auxilar!$B$2:$B$8,FALSE)</f>
         <v>Sábado</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="11">
         <f>_xlfn.XLOOKUP(WEEKDAY(A11),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="1">
+      <c r="D11" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E11" s="12">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="G11" s="12">
+        <v>0.875</v>
+      </c>
+      <c r="H11" s="12">
+        <f t="shared" si="2"/>
+        <v>0.24999999999999994</v>
+      </c>
+      <c r="I11" s="12">
+        <v>0.125</v>
+      </c>
+      <c r="J11" s="14">
+        <f t="shared" si="1"/>
+        <v>2.9999999999999982</v>
+      </c>
+      <c r="K11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" s="10">
         <v>45879</v>
       </c>
-      <c r="B12" t="str">
+      <c r="B12" s="11" t="str">
         <f>_xlfn.XLOOKUP(WEEKDAY(A12),Auxilar!$A$2:$A$8,Auxilar!$B$2:$B$8,FALSE)</f>
         <v>Domingo</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="11">
         <f>_xlfn.XLOOKUP(WEEKDAY(A12),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>45880</v>
       </c>
@@ -3190,8 +3554,34 @@
         <f>_xlfn.XLOOKUP(WEEKDAY(A13),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="D13" s="2">
+        <v>0.31944444444444442</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="H13" s="2">
+        <f t="shared" si="2"/>
+        <v>0.34722222222222232</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J13" s="14">
+        <f t="shared" si="1"/>
+        <v>0.3333333333333357</v>
+      </c>
+      <c r="K13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>45881</v>
       </c>
@@ -3203,8 +3593,34 @@
         <f>_xlfn.XLOOKUP(WEEKDAY(A14),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="D14" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.51388888888888884</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="H14" s="2">
+        <f t="shared" si="2"/>
+        <v>0.38194444444444453</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J14" s="14">
+        <f t="shared" si="1"/>
+        <v>1.1666666666666679</v>
+      </c>
+      <c r="K14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>45882</v>
       </c>
@@ -3216,8 +3632,34 @@
         <f>_xlfn.XLOOKUP(WEEKDAY(A15),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="D15" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="H15" s="2">
+        <f t="shared" si="2"/>
+        <v>0.35416666666666674</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J15" s="14">
+        <f t="shared" si="1"/>
+        <v>0.50000000000000178</v>
+      </c>
+      <c r="K15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>45883</v>
       </c>
@@ -3229,8 +3671,34 @@
         <f>_xlfn.XLOOKUP(WEEKDAY(A16),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="D16" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="H16" s="2">
+        <f t="shared" si="2"/>
+        <v>0.29166666666666674</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J16" s="14">
+        <f t="shared" si="1"/>
+        <v>-0.99999999999999822</v>
+      </c>
+      <c r="K16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>45884</v>
       </c>
@@ -3242,34 +3710,92 @@
         <f>_xlfn.XLOOKUP(WEEKDAY(A17),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="1">
+      <c r="D17" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="H17" s="2">
+        <f t="shared" si="2"/>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J17" s="14">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="K17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18" s="10">
         <v>45885</v>
       </c>
-      <c r="B18" t="str">
+      <c r="B18" s="11" t="str">
         <f>_xlfn.XLOOKUP(WEEKDAY(A18),Auxilar!$A$2:$A$8,Auxilar!$B$2:$B$8,FALSE)</f>
         <v>Sábado</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="11">
         <f>_xlfn.XLOOKUP(WEEKDAY(A18),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="1">
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A19" s="10">
         <v>45886</v>
       </c>
-      <c r="B19" t="str">
+      <c r="B19" s="11" t="str">
         <f>_xlfn.XLOOKUP(WEEKDAY(A19),Auxilar!$A$2:$A$8,Auxilar!$B$2:$B$8,FALSE)</f>
         <v>Domingo</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="11">
         <f>_xlfn.XLOOKUP(WEEKDAY(A19),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I19" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>45887</v>
       </c>
@@ -3281,8 +3807,24 @@
         <f>_xlfn.XLOOKUP(WEEKDAY(A20),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="D20" s="2"/>
+      <c r="H20" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K20" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>45888</v>
       </c>
@@ -3294,8 +3836,34 @@
         <f>_xlfn.XLOOKUP(WEEKDAY(A21),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="D21" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H21" s="2">
+        <f t="shared" si="2"/>
+        <v>0.22916666666666663</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="J21" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K21" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>45889</v>
       </c>
@@ -3307,8 +3875,34 @@
         <f>_xlfn.XLOOKUP(WEEKDAY(A22),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="D22" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G22" s="2">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="H22" s="2">
+        <f t="shared" si="2"/>
+        <v>0.39583333333333343</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="J22" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K22" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>45890</v>
       </c>
@@ -3320,8 +3914,34 @@
         <f>_xlfn.XLOOKUP(WEEKDAY(A23),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="D23" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H23" s="2">
+        <f t="shared" si="2"/>
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="J23" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K23" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>45891</v>
       </c>
@@ -3333,34 +3953,92 @@
         <f>_xlfn.XLOOKUP(WEEKDAY(A24),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="1">
+      <c r="D24" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G24" s="2">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="H24" s="2">
+        <f t="shared" si="2"/>
+        <v>0.41666666666666674</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J24" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K24" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
         <v>45892</v>
       </c>
-      <c r="B25" t="str">
+      <c r="B25" s="11" t="str">
         <f>_xlfn.XLOOKUP(WEEKDAY(A25),Auxilar!$A$2:$A$8,Auxilar!$B$2:$B$8,FALSE)</f>
         <v>Sábado</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="11">
         <f>_xlfn.XLOOKUP(WEEKDAY(A25),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" s="1">
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I25" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
         <v>45893</v>
       </c>
-      <c r="B26" t="str">
+      <c r="B26" s="11" t="str">
         <f>_xlfn.XLOOKUP(WEEKDAY(A26),Auxilar!$A$2:$A$8,Auxilar!$B$2:$B$8,FALSE)</f>
         <v>Domingo</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="11">
         <f>_xlfn.XLOOKUP(WEEKDAY(A26),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>45894</v>
       </c>
@@ -3372,8 +4050,34 @@
         <f>_xlfn.XLOOKUP(WEEKDAY(A27),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="D27" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="H27" s="2">
+        <f t="shared" si="2"/>
+        <v>0.39583333333333337</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="J27" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K27" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>45895</v>
       </c>
@@ -3385,13 +4089,34 @@
         <f>_xlfn.XLOOKUP(WEEKDAY(A28),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="D28" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G28" s="2">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="H28" s="2">
+        <f t="shared" si="2"/>
+        <v>0.39583333333333343</v>
+      </c>
+      <c r="I28" s="2">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="J28" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K28" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>45896</v>
       </c>
@@ -3403,13 +4128,34 @@
         <f>_xlfn.XLOOKUP(WEEKDAY(A29),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="D29" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G29" s="2">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H29" s="2">
+        <f t="shared" si="2"/>
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="J29" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K29" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>45897</v>
       </c>
@@ -3421,13 +4167,34 @@
         <f>_xlfn.XLOOKUP(WEEKDAY(A30),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="D30" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G30" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="H30" s="2">
+        <f t="shared" si="2"/>
+        <v>0.37500000000000006</v>
+      </c>
+      <c r="I30" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J30" s="14">
+        <f t="shared" si="1"/>
+        <v>1.0000000000000018</v>
+      </c>
+      <c r="K30" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>45898</v>
       </c>
@@ -3439,34 +4206,91 @@
         <f>_xlfn.XLOOKUP(WEEKDAY(A31),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A32" s="1">
+      <c r="D31" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G31" s="2">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="H31" s="2">
+        <f t="shared" si="2"/>
+        <v>0.33333333333333343</v>
+      </c>
+      <c r="I31" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J31" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K31" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A32" s="10">
         <v>45899</v>
       </c>
-      <c r="B32" t="str">
+      <c r="B32" s="11" t="str">
         <f>_xlfn.XLOOKUP(WEEKDAY(A32),Auxilar!$A$2:$A$8,Auxilar!$B$2:$B$8,FALSE)</f>
         <v>Sábado</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="11">
         <f>_xlfn.XLOOKUP(WEEKDAY(A32),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A33" s="1">
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I32" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="12"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A33" s="10">
         <v>45900</v>
       </c>
-      <c r="B33" t="str">
+      <c r="B33" s="11" t="str">
         <f>_xlfn.XLOOKUP(WEEKDAY(A33),Auxilar!$A$2:$A$8,Auxilar!$B$2:$B$8,FALSE)</f>
         <v>Domingo</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="11">
         <f>_xlfn.XLOOKUP(WEEKDAY(A33),Auxilar!$A$2:$A$8,Auxilar!$C$2:$C$8,FALSE)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I33" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="12"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>14</v>
       </c>
@@ -3474,9 +4298,33 @@
         <f>SUM(C3:C33)</f>
         <v>21</v>
       </c>
-      <c r="G35" s="2">
-        <f>SUM(G3:G33)</f>
-        <v>0</v>
+      <c r="G35" s="2"/>
+      <c r="H35" s="6">
+        <f>SUM(H3:H33)</f>
+        <v>7.6666666666666679</v>
+      </c>
+      <c r="I35" s="6">
+        <f>SUM(I3:I33)</f>
+        <v>7</v>
+      </c>
+      <c r="K35" s="13"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B37">
+        <f>B35*8</f>
+        <v>168</v>
+      </c>
+      <c r="H37" s="14">
+        <f>H35*24</f>
+        <v>184.00000000000003</v>
+      </c>
+      <c r="I37" s="14">
+        <f>I35*24</f>
+        <v>168</v>
+      </c>
+      <c r="J37" s="14">
+        <f>SUM(J3:J33)</f>
+        <v>16.000000000000014</v>
       </c>
     </row>
   </sheetData>
@@ -5378,11 +6226,11 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
